--- a/examples/output/NL_swissmetro.xlsx
+++ b/examples/output/NL_swissmetro.xlsx
@@ -695,7 +695,7 @@
         <v>20</v>
       </c>
       <c r="B6">
-        <v>1.2540619373321533</v>
+        <v>1.274139165878296</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/NL_swissmetro.xlsx
+++ b/examples/output/NL_swissmetro.xlsx
@@ -695,7 +695,7 @@
         <v>20</v>
       </c>
       <c r="B6">
-        <v>1.274139165878296</v>
+        <v>1.2705121040344238</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/NL_swissmetro.xlsx
+++ b/examples/output/NL_swissmetro.xlsx
@@ -695,7 +695,7 @@
         <v>20</v>
       </c>
       <c r="B6">
-        <v>1.2705121040344238</v>
+        <v>1.3840489387512207</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/NL_swissmetro.xlsx
+++ b/examples/output/NL_swissmetro.xlsx
@@ -695,7 +695,7 @@
         <v>20</v>
       </c>
       <c r="B6">
-        <v>1.3840489387512207</v>
+        <v>1.2708170413970947</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/NL_swissmetro.xlsx
+++ b/examples/output/NL_swissmetro.xlsx
@@ -695,7 +695,7 @@
         <v>20</v>
       </c>
       <c r="B6">
-        <v>1.2708170413970947</v>
+        <v>1.3071739673614502</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/NL_swissmetro.xlsx
+++ b/examples/output/NL_swissmetro.xlsx
@@ -695,7 +695,7 @@
         <v>20</v>
       </c>
       <c r="B6">
-        <v>1.3071739673614502</v>
+        <v>1.3192710876464844</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/NL_swissmetro.xlsx
+++ b/examples/output/NL_swissmetro.xlsx
@@ -695,7 +695,7 @@
         <v>20</v>
       </c>
       <c r="B6">
-        <v>1.3192710876464844</v>
+        <v>1.3451759815216064</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/NL_swissmetro.xlsx
+++ b/examples/output/NL_swissmetro.xlsx
@@ -489,25 +489,25 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>-0.16715562823444824</v>
+        <v>-0.1671556282344138</v>
       </c>
       <c r="C2">
-        <v>0.03713628542877218</v>
+        <v>0.03713628542876606</v>
       </c>
       <c r="D2">
-        <v>-4.501140227259795</v>
+        <v>-4.50114022725961</v>
       </c>
       <c r="E2">
         <v>6.758989416377759e-6</v>
       </c>
       <c r="F2">
-        <v>0.054529059558891</v>
+        <v>0.05452905955889026</v>
       </c>
       <c r="G2">
-        <v>-3.0654412452120385</v>
+        <v>-3.0654412452114483</v>
       </c>
       <c r="H2">
-        <v>0.0021734907743335974</v>
+        <v>0.0021734907743378162</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -541,22 +541,22 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>-0.5119480197705327</v>
+        <v>-0.5119480197697907</v>
       </c>
       <c r="C4">
-        <v>0.04517954370290162</v>
+        <v>0.04517954370288646</v>
       </c>
       <c r="D4">
-        <v>-11.33141191369875</v>
+        <v>-11.331411913686127</v>
       </c>
       <c r="E4">
         <v>0.0</v>
       </c>
       <c r="F4">
-        <v>0.07911361900380866</v>
+        <v>0.07911361900379331</v>
       </c>
       <c r="G4">
-        <v>-6.471047920913423</v>
+        <v>-6.471047920905299</v>
       </c>
       <c r="H4">
         <v>9.73254810077151e-11</v>
@@ -567,22 +567,22 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>-0.8566652828279274</v>
+        <v>-0.856665282828324</v>
       </c>
       <c r="C5">
-        <v>0.046273103144332736</v>
+        <v>0.046273103144352845</v>
       </c>
       <c r="D5">
-        <v>-18.51324472784676</v>
+        <v>-18.513244727847287</v>
       </c>
       <c r="E5">
         <v>0.0</v>
       </c>
       <c r="F5">
-        <v>0.06003512366455625</v>
+        <v>0.060035123664609245</v>
       </c>
       <c r="G5">
-        <v>-14.269401485945277</v>
+        <v>-14.269401485939287</v>
       </c>
       <c r="H5">
         <v>0.0</v>
@@ -593,22 +593,22 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>-0.8986638075522556</v>
+        <v>-0.898663807552445</v>
       </c>
       <c r="C6">
-        <v>0.05699063461260376</v>
+        <v>0.056990634612613986</v>
       </c>
       <c r="D6">
-        <v>-15.768622575638274</v>
+        <v>-15.768622575638767</v>
       </c>
       <c r="E6">
         <v>0.0</v>
       </c>
       <c r="F6">
-        <v>0.10711249893442112</v>
+        <v>0.10711249893446544</v>
       </c>
       <c r="G6">
-        <v>-8.389906093988678</v>
+        <v>-8.389906093986976</v>
       </c>
       <c r="H6">
         <v>0.0</v>
@@ -619,22 +619,22 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>0.4868393942872666</v>
+        <v>0.48683939428700657</v>
       </c>
       <c r="C7">
-        <v>0.027897465370017322</v>
+        <v>0.027897465369998365</v>
       </c>
       <c r="D7">
-        <v>17.451026027995184</v>
+        <v>17.45102602799772</v>
       </c>
       <c r="E7">
         <v>0.0</v>
       </c>
       <c r="F7">
-        <v>0.03891834131747491</v>
+        <v>0.03891834131744846</v>
       </c>
       <c r="G7">
-        <v>12.509253421565234</v>
+        <v>12.509253421567054</v>
       </c>
       <c r="H7">
         <v>0.0</v>
@@ -655,7 +655,7 @@
         <v>14</v>
       </c>
       <c r="B1">
-        <v>-5236.900013578784</v>
+        <v>-5236.900013578785</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -695,7 +695,7 @@
         <v>20</v>
       </c>
       <c r="B6">
-        <v>1.3451759815216064</v>
+        <v>1.3640520572662354</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -719,7 +719,7 @@
         <v>23</v>
       </c>
       <c r="B9">
-        <v>10483.800027157567</v>
+        <v>10483.80002715757</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -727,7 +727,7 @@
         <v>24</v>
       </c>
       <c r="B10">
-        <v>10517.899831663997</v>
+        <v>10517.899831663999</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -735,7 +735,7 @@
         <v>25</v>
       </c>
       <c r="B11">
-        <v>0.24807560262065353</v>
+        <v>0.24807560262065342</v>
       </c>
     </row>
   </sheetData>

--- a/examples/output/NL_swissmetro.xlsx
+++ b/examples/output/NL_swissmetro.xlsx
@@ -695,7 +695,7 @@
         <v>20</v>
       </c>
       <c r="B6">
-        <v>1.3640520572662354</v>
+        <v>1.3193740844726562</v>
       </c>
     </row>
     <row r="7" spans="1:2">
